--- a/서버정보/20261002_리소스배포_테스트.xlsx
+++ b/서버정보/20261002_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8F2944-80E3-4225-AFB0-FA7C25158BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFEB697-4800-4E49-8562-242056A45A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -3958,22 +3958,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>t-tm-db-nsg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-tm-pe-nsg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-ga-db-nsg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-ga-pe-nsg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t-bsu-db-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4019,6 +4003,22 @@
   </si>
   <si>
     <t>10.157.171.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-tm-db-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-tm-pe-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-ga-db-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-ga-pe-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4516,7 +4516,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4873,9 +4873,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11120,7 +11117,7 @@
         <v>607</v>
       </c>
       <c r="D71" s="74" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E71" s="74" t="str">
         <f t="shared" si="24"/>
@@ -11181,7 +11178,7 @@
         <v>607</v>
       </c>
       <c r="D72" s="84" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E72" s="84" t="str">
         <f t="shared" ref="E72:E75" si="42">SUBSTITUTE(D72, "hazr-", "")&amp;"-rule"&amp;N72</f>
@@ -11242,7 +11239,7 @@
         <v>607</v>
       </c>
       <c r="D73" s="74" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E73" s="74" t="str">
         <f t="shared" si="42"/>
@@ -11303,7 +11300,7 @@
         <v>608</v>
       </c>
       <c r="D74" s="84" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="E74" s="84" t="str">
         <f t="shared" si="42"/>
@@ -11364,7 +11361,7 @@
         <v>608</v>
       </c>
       <c r="D75" s="74" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E75" s="74" t="str">
         <f t="shared" si="42"/>
@@ -17183,6 +17180,7 @@
       <c r="AF62" s="113"/>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A63" s="97"/>
       <c r="B63" s="107" t="s">
         <v>182</v>
       </c>
@@ -17271,6 +17269,7 @@
       <c r="AF63" s="107"/>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A64" s="97"/>
       <c r="B64" s="113" t="s">
         <v>182</v>
       </c>
@@ -17358,7 +17357,8 @@
       <c r="AE64" s="113"/>
       <c r="AF64" s="113"/>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A65" s="97"/>
       <c r="B65" s="113" t="s">
         <v>182</v>
       </c>
@@ -17446,7 +17446,8 @@
       <c r="AE65" s="113"/>
       <c r="AF65" s="113"/>
     </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A66" s="97"/>
       <c r="B66" s="113" t="s">
         <v>182</v>
       </c>
@@ -17534,7 +17535,8 @@
       <c r="AE66" s="113"/>
       <c r="AF66" s="113"/>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A67" s="97"/>
       <c r="B67" s="113" t="s">
         <v>182</v>
       </c>
@@ -21066,6 +21068,7 @@
       <c r="R62" s="74"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" s="98"/>
       <c r="B63" s="73" t="s">
         <v>182</v>
       </c>
@@ -21120,6 +21123,7 @@
       <c r="R63" s="73"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A64" s="98"/>
       <c r="B64" s="74" t="s">
         <v>182</v>
       </c>
@@ -21173,7 +21177,8 @@
       </c>
       <c r="R64" s="74"/>
     </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A65" s="98"/>
       <c r="B65" s="73" t="s">
         <v>182</v>
       </c>
@@ -21227,7 +21232,8 @@
       </c>
       <c r="R65" s="73"/>
     </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A66" s="98"/>
       <c r="B66" s="74" t="s">
         <v>182</v>
       </c>
@@ -21281,7 +21287,8 @@
       </c>
       <c r="R66" s="74"/>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A67" s="98"/>
       <c r="B67" s="73" t="s">
         <v>182</v>
       </c>
@@ -23424,7 +23431,7 @@
       <c r="M52" s="73"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" s="119"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="82" t="s">
         <v>182</v>
       </c>
@@ -23446,7 +23453,7 @@
         <v>450</v>
       </c>
       <c r="H53" s="74" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="I53" s="74"/>
       <c r="J53" s="74"/>
@@ -23457,7 +23464,7 @@
       <c r="M53" s="74"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" s="119"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="80" t="s">
         <v>182</v>
       </c>
@@ -23479,7 +23486,7 @@
         <v>450</v>
       </c>
       <c r="H54" s="73" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="I54" s="73"/>
       <c r="J54" s="73"/>
@@ -23950,7 +23957,7 @@
       <c r="M68" s="73"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A69" s="119"/>
+      <c r="A69" s="97"/>
       <c r="B69" s="82" t="s">
         <v>182</v>
       </c>
@@ -23963,7 +23970,7 @@
       </c>
       <c r="E69" s="82" t="str">
         <f t="shared" si="4"/>
-        <v>t-tm-db-nsg-nsg</v>
+        <v>t-tm-db-nsg</v>
       </c>
       <c r="F69" s="82" t="s">
         <v>198</v>
@@ -23972,7 +23979,7 @@
         <v>200</v>
       </c>
       <c r="H69" s="74" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="I69" s="74"/>
       <c r="J69" s="74"/>
@@ -23983,7 +23990,7 @@
       <c r="M69" s="74"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A70" s="119"/>
+      <c r="A70" s="97"/>
       <c r="B70" s="80" t="s">
         <v>182</v>
       </c>
@@ -23995,8 +24002,8 @@
         <v>198</v>
       </c>
       <c r="E70" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>t-tm-pe-nsg-nsg</v>
+        <f>SUBSTITUTE(H70,"-sbn","")&amp;"-nsg"</f>
+        <v>t-tm-pe-nsg</v>
       </c>
       <c r="F70" s="80" t="s">
         <v>198</v>
@@ -24005,7 +24012,7 @@
         <v>450</v>
       </c>
       <c r="H70" s="73" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="I70" s="73"/>
       <c r="J70" s="73"/>
@@ -24016,7 +24023,7 @@
       <c r="M70" s="73"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A71" s="119"/>
+      <c r="A71" s="97"/>
       <c r="B71" s="82" t="s">
         <v>182</v>
       </c>
@@ -24029,7 +24036,7 @@
       </c>
       <c r="E71" s="82" t="str">
         <f t="shared" si="4"/>
-        <v>t-ga-db-nsg-nsg</v>
+        <v>t-ga-db-nsg</v>
       </c>
       <c r="F71" s="82" t="s">
         <v>198</v>
@@ -24038,7 +24045,7 @@
         <v>200</v>
       </c>
       <c r="H71" s="74" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="I71" s="74"/>
       <c r="J71" s="74"/>
@@ -24049,7 +24056,7 @@
       <c r="M71" s="74"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A72" s="119"/>
+      <c r="A72" s="97"/>
       <c r="B72" s="80" t="s">
         <v>182</v>
       </c>
@@ -24062,7 +24069,7 @@
       </c>
       <c r="E72" s="80" t="str">
         <f t="shared" si="4"/>
-        <v>t-ga-pe-nsg-nsg</v>
+        <v>t-ga-pe-nsg</v>
       </c>
       <c r="F72" s="80" t="s">
         <v>198</v>
@@ -24071,7 +24078,7 @@
         <v>450</v>
       </c>
       <c r="H72" s="73" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="I72" s="73"/>
       <c r="J72" s="73"/>
@@ -24576,6 +24583,7 @@
       <c r="M84" s="73"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="97"/>
       <c r="B85" s="82" t="s">
         <v>182</v>
       </c>
@@ -24615,6 +24623,7 @@
       <c r="M85" s="74"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="97"/>
       <c r="B86" s="80" t="s">
         <v>182</v>
       </c>
@@ -24654,6 +24663,7 @@
       <c r="M86" s="73"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="97"/>
       <c r="B87" s="82" t="s">
         <v>182</v>
       </c>
@@ -24693,6 +24703,7 @@
       <c r="M87" s="74"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="97"/>
       <c r="B88" s="80" t="s">
         <v>182</v>
       </c>
@@ -24732,6 +24743,7 @@
       <c r="M88" s="73"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="97"/>
       <c r="B89" s="82" t="s">
         <v>182</v>
       </c>
@@ -29665,7 +29677,7 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="69"/>
       <c r="B46" s="74" t="s">
         <v>182</v>
       </c>
@@ -29680,7 +29692,7 @@
         <v>24</v>
       </c>
       <c r="F46" s="74" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G46" s="74" t="s">
         <v>111</v>
@@ -29711,7 +29723,7 @@
         <v>108</v>
       </c>
       <c r="P46" s="74" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="Q46" s="74" t="str">
         <f t="shared" si="5"/>
@@ -29719,7 +29731,7 @@
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
+      <c r="A47" s="69"/>
       <c r="B47" s="84" t="s">
         <v>182</v>
       </c>
@@ -29734,7 +29746,7 @@
         <v>24</v>
       </c>
       <c r="F47" s="84" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="G47" s="84" t="s">
         <v>111</v>
@@ -29765,7 +29777,7 @@
         <v>108</v>
       </c>
       <c r="P47" s="84" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="Q47" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29773,7 +29785,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+      <c r="A48" s="69"/>
       <c r="B48" s="74" t="s">
         <v>182</v>
       </c>
@@ -29788,7 +29800,7 @@
         <v>24</v>
       </c>
       <c r="F48" s="74" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G48" s="74" t="s">
         <v>111</v>
@@ -29819,7 +29831,7 @@
         <v>108</v>
       </c>
       <c r="P48" s="74" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="Q48" s="74" t="str">
         <f t="shared" si="5"/>
@@ -29827,7 +29839,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
+      <c r="A49" s="69"/>
       <c r="B49" s="84" t="s">
         <v>182</v>
       </c>
@@ -29842,7 +29854,7 @@
         <v>24</v>
       </c>
       <c r="F49" s="84" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="G49" s="84" t="s">
         <v>111</v>
@@ -29873,7 +29885,7 @@
         <v>108</v>
       </c>
       <c r="P49" s="84" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="Q49" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29881,7 +29893,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
+      <c r="A50" s="69"/>
       <c r="B50" s="74" t="s">
         <v>182</v>
       </c>
@@ -29896,7 +29908,7 @@
         <v>24</v>
       </c>
       <c r="F50" s="74" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="G50" s="74" t="s">
         <v>111</v>
@@ -29927,7 +29939,7 @@
         <v>108</v>
       </c>
       <c r="P50" s="74" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="Q50" s="74" t="str">
         <f t="shared" si="5"/>
@@ -32230,7 +32242,7 @@
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="48"/>
+      <c r="A71" s="69"/>
       <c r="B71" s="74" t="s">
         <v>182</v>
       </c>
@@ -32242,7 +32254,7 @@
         <v>607</v>
       </c>
       <c r="E71" s="74" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="F71" s="74" t="str">
         <f t="shared" si="5"/>
@@ -32263,7 +32275,7 @@
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="48"/>
+      <c r="A72" s="69"/>
       <c r="B72" s="84" t="s">
         <v>182</v>
       </c>
@@ -32275,7 +32287,7 @@
         <v>607</v>
       </c>
       <c r="E72" s="84" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F72" s="84" t="str">
         <f t="shared" si="5"/>
@@ -32296,7 +32308,7 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="48"/>
+      <c r="A73" s="69"/>
       <c r="B73" s="74" t="s">
         <v>182</v>
       </c>
@@ -32308,7 +32320,7 @@
         <v>607</v>
       </c>
       <c r="E73" s="74" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F73" s="74" t="str">
         <f t="shared" si="5"/>
@@ -32329,7 +32341,7 @@
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="48"/>
+      <c r="A74" s="69"/>
       <c r="B74" s="84" t="s">
         <v>182</v>
       </c>
@@ -32341,7 +32353,7 @@
         <v>608</v>
       </c>
       <c r="E74" s="84" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F74" s="84" t="str">
         <f t="shared" si="5"/>
@@ -32362,7 +32374,7 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="48"/>
+      <c r="A75" s="69"/>
       <c r="B75" s="74" t="s">
         <v>182</v>
       </c>
@@ -32374,7 +32386,7 @@
         <v>608</v>
       </c>
       <c r="E75" s="74" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="F75" s="74" t="str">
         <f t="shared" si="5"/>
@@ -32401,21 +32413,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32559,31 +32556,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32599,4 +32587,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>